--- a/04_Network/04_Associate/c_data/04_associate.xlsx
+++ b/04_Network/04_Associate/c_data/04_associate.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10028" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10093" uniqueCount="235">
   <si>
     <t>sheet</t>
   </si>
@@ -56,7 +56,7 @@
     <t>plot_index</t>
   </si>
   <si>
-    <t>PDF page and panel position (1 to 12) of every p &lt; 0.05 model and change-score row.</t>
+    <t>PDF page of each overview, and page and panel position of every p &lt; 0.05 row.</t>
   </si>
   <si>
     <t>input_manifest</t>
@@ -293,6 +293,21 @@
     <t>position</t>
   </si>
   <si>
+    <t>overview</t>
+  </si>
+  <si>
+    <t>Sample model overview: modules</t>
+  </si>
+  <si>
+    <t>Change score overview, training window: modules</t>
+  </si>
+  <si>
+    <t>Change score overview, baseline window: modules</t>
+  </si>
+  <si>
+    <t>Change score overview, acute window: modules</t>
+  </si>
+  <si>
     <t>change score</t>
   </si>
   <si>
@@ -332,6 +347,15 @@
     <t>source</t>
   </si>
   <si>
+    <t>BiocGenerics</t>
+  </si>
+  <si>
+    <t>0.58.0</t>
+  </si>
+  <si>
+    <t>Bioconductor 3.23 (R 4.6.0)</t>
+  </si>
+  <si>
     <t>BiocManager</t>
   </si>
   <si>
@@ -353,16 +377,64 @@
     <t>4.8.0</t>
   </si>
   <si>
+    <t>circlize</t>
+  </si>
+  <si>
+    <t>0.4.18</t>
+  </si>
+  <si>
     <t>cli</t>
   </si>
   <si>
     <t>3.6.6</t>
   </si>
   <si>
+    <t>clue</t>
+  </si>
+  <si>
+    <t>0.3-68</t>
+  </si>
+  <si>
+    <t>cluster</t>
+  </si>
+  <si>
+    <t>2.1.8.2</t>
+  </si>
+  <si>
+    <t>codetools</t>
+  </si>
+  <si>
+    <t>0.2-20</t>
+  </si>
+  <si>
+    <t>colorspace</t>
+  </si>
+  <si>
+    <t>2.1-2</t>
+  </si>
+  <si>
+    <t>ComplexHeatmap</t>
+  </si>
+  <si>
+    <t>2.28.0</t>
+  </si>
+  <si>
     <t>crayon</t>
   </si>
   <si>
     <t>1.5.3</t>
+  </si>
+  <si>
+    <t>digest</t>
+  </si>
+  <si>
+    <t>0.6.39</t>
+  </si>
+  <si>
+    <t>doParallel</t>
+  </si>
+  <si>
+    <t>1.0.17</t>
   </si>
   <si>
     <t>dplyr</t>
@@ -377,16 +449,31 @@
     <t>2.1.2</t>
   </si>
   <si>
+    <t>foreach</t>
+  </si>
+  <si>
+    <t>1.5.2</t>
+  </si>
+  <si>
     <t>generics</t>
   </si>
   <si>
     <t>0.1.4</t>
   </si>
   <si>
+    <t>GetoptLong</t>
+  </si>
+  <si>
+    <t>1.1.1</t>
+  </si>
+  <si>
     <t>ggplot2</t>
   </si>
   <si>
     <t>4.0.3</t>
+  </si>
+  <si>
+    <t>GlobalOptions</t>
   </si>
   <si>
     <t>glue</t>
@@ -413,6 +500,18 @@
     <t>1.1.4</t>
   </si>
   <si>
+    <t>IRanges</t>
+  </si>
+  <si>
+    <t>2.46.0</t>
+  </si>
+  <si>
+    <t>iterators</t>
+  </si>
+  <si>
+    <t>1.0.14</t>
+  </si>
+  <si>
     <t>labeling</t>
   </si>
   <si>
@@ -437,9 +536,6 @@
     <t>3.68.1</t>
   </si>
   <si>
-    <t>Bioconductor 3.23 (R 4.6.0)</t>
-  </si>
-  <si>
     <t>magrittr</t>
   </si>
   <si>
@@ -450,6 +546,12 @@
   </si>
   <si>
     <t>1.7-5</t>
+  </si>
+  <si>
+    <t>matrixStats</t>
+  </si>
+  <si>
+    <t>1.5.0</t>
   </si>
   <si>
     <t>mgcv</t>
@@ -474,6 +576,12 @@
   </si>
   <si>
     <t>2.0.3</t>
+  </si>
+  <si>
+    <t>png</t>
+  </si>
+  <si>
+    <t>0.1-9</t>
   </si>
   <si>
     <t>purrr</t>
@@ -506,6 +614,12 @@
     <t>1.2.3</t>
   </si>
   <si>
+    <t>rjson</t>
+  </si>
+  <si>
+    <t>0.2.23</t>
+  </si>
+  <si>
     <t>rlang</t>
   </si>
   <si>
@@ -519,6 +633,12 @@
   </si>
   <si>
     <t>2.1.1</t>
+  </si>
+  <si>
+    <t>S4Vectors</t>
+  </si>
+  <si>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>S7</t>
@@ -537,6 +657,12 @@
   </si>
   <si>
     <t>1.2.4</t>
+  </si>
+  <si>
+    <t>shape</t>
+  </si>
+  <si>
+    <t>1.4.6.1</t>
   </si>
   <si>
     <t>statmod</t>
@@ -60581,7 +60707,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1">
@@ -60589,19 +60715,19 @@
         <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>88</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>89</v>
@@ -60615,94 +60741,46 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>90</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
+        <v>91</v>
+      </c>
+      <c r="C2">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>90</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F3">
+        <v>92</v>
+      </c>
+      <c r="C3">
         <v>2</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>90</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E4" t="s">
-        <v>73</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
+        <v>93</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C5">
         <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D5" t="s">
-        <v>70</v>
-      </c>
-      <c r="E5" t="s">
-        <v>70</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -60710,22 +60788,22 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
         <v>64</v>
       </c>
-      <c r="D6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E6" t="s">
-        <v>76</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
+      <c r="F6" t="s">
+        <v>65</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -60733,19 +60811,19 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" t="s">
-        <v>77</v>
+        <v>75</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="E7" t="s">
-        <v>74</v>
-      </c>
-      <c r="F7">
-        <v>3</v>
+        <v>64</v>
+      </c>
+      <c r="F7" t="s">
+        <v>75</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -60756,19 +60834,19 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" t="s">
-        <v>77</v>
+        <v>73</v>
+      </c>
+      <c r="C8">
+        <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="E8" t="s">
-        <v>71</v>
-      </c>
-      <c r="F8">
-        <v>3</v>
+        <v>64</v>
+      </c>
+      <c r="F8" t="s">
+        <v>73</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -60779,22 +60857,22 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+      <c r="D9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" t="s">
         <v>64</v>
       </c>
-      <c r="D9" t="s">
-        <v>75</v>
-      </c>
-      <c r="E9" t="s">
-        <v>75</v>
-      </c>
-      <c r="F9">
-        <v>4</v>
+      <c r="F9" t="s">
+        <v>70</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -60802,157 +60880,157 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" t="s">
-        <v>77</v>
+        <v>76</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
       </c>
       <c r="D10" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="E10" t="s">
-        <v>72</v>
-      </c>
-      <c r="F10">
-        <v>5</v>
+        <v>64</v>
+      </c>
+      <c r="F10" t="s">
+        <v>76</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>90</v>
+        <v>4</v>
+      </c>
+      <c r="B11" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
       </c>
       <c r="D11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" t="s">
+        <v>77</v>
+      </c>
+      <c r="F11" t="s">
         <v>74</v>
-      </c>
-      <c r="E11" t="s">
-        <v>74</v>
-      </c>
-      <c r="F11">
-        <v>6</v>
       </c>
       <c r="G11">
         <v>1</v>
       </c>
-      <c r="H11" t="s">
-        <v>84</v>
-      </c>
-      <c r="I11" t="s">
-        <v>42</v>
-      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>90</v>
+        <v>4</v>
+      </c>
+      <c r="B12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12">
+        <v>7</v>
       </c>
       <c r="D12" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="E12" t="s">
-        <v>72</v>
-      </c>
-      <c r="F12">
-        <v>6</v>
+        <v>77</v>
+      </c>
+      <c r="F12" t="s">
+        <v>71</v>
       </c>
       <c r="G12">
         <v>2</v>
       </c>
-      <c r="H12" t="s">
-        <v>84</v>
-      </c>
-      <c r="I12" t="s">
-        <v>52</v>
-      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>90</v>
+        <v>4</v>
+      </c>
+      <c r="B13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13">
+        <v>8</v>
       </c>
       <c r="D13" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="E13" t="s">
-        <v>72</v>
-      </c>
-      <c r="F13">
-        <v>6</v>
+        <v>64</v>
+      </c>
+      <c r="F13" t="s">
+        <v>75</v>
       </c>
       <c r="G13">
-        <v>3</v>
-      </c>
-      <c r="H13" t="s">
-        <v>84</v>
-      </c>
-      <c r="I13" t="s">
-        <v>43</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>90</v>
+        <v>4</v>
+      </c>
+      <c r="B14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14">
+        <v>9</v>
       </c>
       <c r="D14" t="s">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="E14" t="s">
-        <v>71</v>
-      </c>
-      <c r="F14">
-        <v>6</v>
+        <v>77</v>
+      </c>
+      <c r="F14" t="s">
+        <v>72</v>
       </c>
       <c r="G14">
-        <v>4</v>
-      </c>
-      <c r="H14" t="s">
-        <v>84</v>
-      </c>
-      <c r="I14" t="s">
-        <v>42</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>90</v>
-      </c>
-      <c r="D15" t="s">
-        <v>75</v>
-      </c>
-      <c r="E15" t="s">
-        <v>75</v>
-      </c>
-      <c r="F15">
-        <v>6</v>
+        <v>95</v>
+      </c>
+      <c r="B15" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>74</v>
       </c>
       <c r="G15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H15" t="s">
         <v>84</v>
       </c>
       <c r="I15" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>90</v>
-      </c>
-      <c r="D16" t="s">
+        <v>95</v>
+      </c>
+      <c r="B16" t="s">
         <v>72</v>
       </c>
-      <c r="E16" t="s">
+      <c r="C16">
+        <v>10</v>
+      </c>
+      <c r="F16" t="s">
         <v>72</v>
       </c>
-      <c r="F16">
-        <v>7</v>
-      </c>
       <c r="G16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I16" t="s">
         <v>52</v>
@@ -60960,22 +61038,22 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>90</v>
-      </c>
-      <c r="D17" t="s">
+        <v>95</v>
+      </c>
+      <c r="B17" t="s">
         <v>72</v>
       </c>
-      <c r="E17" t="s">
+      <c r="C17">
+        <v>10</v>
+      </c>
+      <c r="F17" t="s">
         <v>72</v>
       </c>
-      <c r="F17">
-        <v>7</v>
-      </c>
       <c r="G17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I17" t="s">
         <v>43</v>
@@ -60983,22 +61061,22 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>90</v>
-      </c>
-      <c r="D18" t="s">
+        <v>95</v>
+      </c>
+      <c r="B18" t="s">
         <v>71</v>
       </c>
-      <c r="E18" t="s">
+      <c r="C18">
+        <v>10</v>
+      </c>
+      <c r="F18" t="s">
         <v>71</v>
       </c>
-      <c r="F18">
-        <v>7</v>
-      </c>
       <c r="G18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H18" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I18" t="s">
         <v>42</v>
@@ -61006,392 +61084,484 @@
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>90</v>
-      </c>
-      <c r="D19" t="s">
+        <v>95</v>
+      </c>
+      <c r="B19" t="s">
         <v>75</v>
       </c>
-      <c r="E19" t="s">
+      <c r="C19">
+        <v>10</v>
+      </c>
+      <c r="F19" t="s">
         <v>75</v>
       </c>
-      <c r="F19">
-        <v>7</v>
-      </c>
       <c r="G19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I19" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>90</v>
-      </c>
-      <c r="D20" t="s">
-        <v>74</v>
-      </c>
-      <c r="E20" t="s">
-        <v>74</v>
-      </c>
-      <c r="F20">
-        <v>7</v>
+        <v>95</v>
+      </c>
+      <c r="B20" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20">
+        <v>11</v>
+      </c>
+      <c r="F20" t="s">
+        <v>72</v>
       </c>
       <c r="G20">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H20" t="s">
         <v>83</v>
       </c>
       <c r="I20" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>90</v>
-      </c>
-      <c r="D21" t="s">
-        <v>75</v>
-      </c>
-      <c r="E21" t="s">
-        <v>75</v>
-      </c>
-      <c r="F21">
-        <v>7</v>
+        <v>95</v>
+      </c>
+      <c r="B21" t="s">
+        <v>72</v>
+      </c>
+      <c r="C21">
+        <v>11</v>
+      </c>
+      <c r="F21" t="s">
+        <v>72</v>
       </c>
       <c r="G21">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H21" t="s">
         <v>83</v>
       </c>
       <c r="I21" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>90</v>
-      </c>
-      <c r="D22" t="s">
-        <v>76</v>
-      </c>
-      <c r="E22" t="s">
-        <v>76</v>
-      </c>
-      <c r="F22">
-        <v>7</v>
+        <v>95</v>
+      </c>
+      <c r="B22" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22">
+        <v>11</v>
+      </c>
+      <c r="F22" t="s">
+        <v>71</v>
       </c>
       <c r="G22">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H22" t="s">
         <v>83</v>
       </c>
       <c r="I22" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>90</v>
-      </c>
-      <c r="D23" t="s">
-        <v>73</v>
-      </c>
-      <c r="E23" t="s">
-        <v>73</v>
-      </c>
-      <c r="F23">
-        <v>7</v>
+        <v>95</v>
+      </c>
+      <c r="B23" t="s">
+        <v>75</v>
+      </c>
+      <c r="C23">
+        <v>11</v>
+      </c>
+      <c r="F23" t="s">
+        <v>75</v>
       </c>
       <c r="G23">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H23" t="s">
         <v>83</v>
       </c>
       <c r="I23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>90</v>
-      </c>
-      <c r="D24" t="s">
-        <v>73</v>
-      </c>
-      <c r="E24" t="s">
-        <v>73</v>
-      </c>
-      <c r="F24">
-        <v>7</v>
+        <v>95</v>
+      </c>
+      <c r="B24" t="s">
+        <v>74</v>
+      </c>
+      <c r="C24">
+        <v>11</v>
+      </c>
+      <c r="F24" t="s">
+        <v>74</v>
       </c>
       <c r="G24">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H24" t="s">
         <v>83</v>
       </c>
       <c r="I24" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>90</v>
-      </c>
-      <c r="D25" t="s">
-        <v>74</v>
-      </c>
-      <c r="E25" t="s">
-        <v>74</v>
-      </c>
-      <c r="F25">
-        <v>7</v>
+        <v>95</v>
+      </c>
+      <c r="B25" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25">
+        <v>11</v>
+      </c>
+      <c r="F25" t="s">
+        <v>75</v>
       </c>
       <c r="G25">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H25" t="s">
         <v>83</v>
       </c>
       <c r="I25" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" t="s">
-        <v>90</v>
-      </c>
-      <c r="D26" t="s">
-        <v>71</v>
-      </c>
-      <c r="E26" t="s">
-        <v>71</v>
-      </c>
-      <c r="F26">
+        <v>95</v>
+      </c>
+      <c r="B26" t="s">
+        <v>76</v>
+      </c>
+      <c r="C26">
+        <v>11</v>
+      </c>
+      <c r="F26" t="s">
+        <v>76</v>
+      </c>
+      <c r="G26">
         <v>7</v>
       </c>
-      <c r="G26">
-        <v>11</v>
-      </c>
       <c r="H26" t="s">
         <v>83</v>
       </c>
       <c r="I26" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>90</v>
-      </c>
-      <c r="D27" t="s">
-        <v>74</v>
-      </c>
-      <c r="E27" t="s">
-        <v>74</v>
-      </c>
-      <c r="F27">
-        <v>7</v>
+        <v>95</v>
+      </c>
+      <c r="B27" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27">
+        <v>11</v>
+      </c>
+      <c r="F27" t="s">
+        <v>73</v>
       </c>
       <c r="G27">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H27" t="s">
         <v>83</v>
       </c>
       <c r="I27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>90</v>
-      </c>
-      <c r="D28" t="s">
-        <v>68</v>
-      </c>
-      <c r="E28" t="s">
-        <v>68</v>
-      </c>
-      <c r="F28">
-        <v>8</v>
+        <v>95</v>
+      </c>
+      <c r="B28" t="s">
+        <v>73</v>
+      </c>
+      <c r="C28">
+        <v>11</v>
+      </c>
+      <c r="F28" t="s">
+        <v>73</v>
       </c>
       <c r="G28">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H28" t="s">
         <v>83</v>
       </c>
       <c r="I28" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>90</v>
-      </c>
-      <c r="D29" t="s">
+        <v>95</v>
+      </c>
+      <c r="B29" t="s">
         <v>74</v>
       </c>
-      <c r="E29" t="s">
+      <c r="C29">
+        <v>11</v>
+      </c>
+      <c r="F29" t="s">
         <v>74</v>
       </c>
-      <c r="F29">
-        <v>9</v>
-      </c>
       <c r="G29">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H29" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I29" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>90</v>
-      </c>
-      <c r="D30" t="s">
-        <v>75</v>
-      </c>
-      <c r="E30" t="s">
-        <v>75</v>
-      </c>
-      <c r="F30">
-        <v>9</v>
+        <v>95</v>
+      </c>
+      <c r="B30" t="s">
+        <v>71</v>
+      </c>
+      <c r="C30">
+        <v>11</v>
+      </c>
+      <c r="F30" t="s">
+        <v>71</v>
       </c>
       <c r="G30">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H30" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I30" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>90</v>
-      </c>
-      <c r="D31" t="s">
-        <v>71</v>
-      </c>
-      <c r="E31" t="s">
-        <v>71</v>
-      </c>
-      <c r="F31">
-        <v>9</v>
+        <v>95</v>
+      </c>
+      <c r="B31" t="s">
+        <v>74</v>
+      </c>
+      <c r="C31">
+        <v>11</v>
+      </c>
+      <c r="F31" t="s">
+        <v>74</v>
       </c>
       <c r="G31">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H31" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I31" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>90</v>
-      </c>
-      <c r="D32" t="s">
-        <v>71</v>
-      </c>
-      <c r="E32" t="s">
-        <v>71</v>
-      </c>
-      <c r="F32">
-        <v>9</v>
+        <v>95</v>
+      </c>
+      <c r="B32" t="s">
+        <v>68</v>
+      </c>
+      <c r="C32">
+        <v>12</v>
+      </c>
+      <c r="F32" t="s">
+        <v>68</v>
       </c>
       <c r="G32">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H32" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I32" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" t="s">
-        <v>90</v>
-      </c>
-      <c r="D33" t="s">
+        <v>95</v>
+      </c>
+      <c r="B33" t="s">
         <v>74</v>
       </c>
-      <c r="E33" t="s">
+      <c r="C33">
+        <v>13</v>
+      </c>
+      <c r="F33" t="s">
         <v>74</v>
       </c>
-      <c r="F33">
-        <v>9</v>
-      </c>
       <c r="G33">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H33" t="s">
         <v>82</v>
       </c>
       <c r="I33" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" t="s">
-        <v>90</v>
-      </c>
-      <c r="D34" t="s">
-        <v>73</v>
-      </c>
-      <c r="E34" t="s">
-        <v>73</v>
-      </c>
-      <c r="F34">
-        <v>9</v>
+        <v>95</v>
+      </c>
+      <c r="B34" t="s">
+        <v>75</v>
+      </c>
+      <c r="C34">
+        <v>13</v>
+      </c>
+      <c r="F34" t="s">
+        <v>75</v>
       </c>
       <c r="G34">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H34" t="s">
         <v>82</v>
       </c>
       <c r="I34" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>90</v>
-      </c>
-      <c r="D35" t="s">
+        <v>95</v>
+      </c>
+      <c r="B35" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35">
+        <v>13</v>
+      </c>
+      <c r="F35" t="s">
+        <v>71</v>
+      </c>
+      <c r="G35">
+        <v>3</v>
+      </c>
+      <c r="H35" t="s">
+        <v>82</v>
+      </c>
+      <c r="I35" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" t="s">
+        <v>95</v>
+      </c>
+      <c r="B36" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36">
+        <v>13</v>
+      </c>
+      <c r="F36" t="s">
+        <v>71</v>
+      </c>
+      <c r="G36">
+        <v>4</v>
+      </c>
+      <c r="H36" t="s">
+        <v>82</v>
+      </c>
+      <c r="I36" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" t="s">
+        <v>95</v>
+      </c>
+      <c r="B37" t="s">
         <v>74</v>
       </c>
-      <c r="E35" t="s">
+      <c r="C37">
+        <v>13</v>
+      </c>
+      <c r="F37" t="s">
         <v>74</v>
       </c>
-      <c r="F35">
-        <v>9</v>
-      </c>
-      <c r="G35">
+      <c r="G37">
+        <v>5</v>
+      </c>
+      <c r="H37" t="s">
+        <v>82</v>
+      </c>
+      <c r="I37" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" t="s">
+        <v>95</v>
+      </c>
+      <c r="B38" t="s">
+        <v>73</v>
+      </c>
+      <c r="C38">
+        <v>13</v>
+      </c>
+      <c r="F38" t="s">
+        <v>73</v>
+      </c>
+      <c r="G38">
+        <v>6</v>
+      </c>
+      <c r="H38" t="s">
+        <v>82</v>
+      </c>
+      <c r="I38" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" t="s">
+        <v>95</v>
+      </c>
+      <c r="B39" t="s">
+        <v>74</v>
+      </c>
+      <c r="C39">
+        <v>13</v>
+      </c>
+      <c r="F39" t="s">
+        <v>74</v>
+      </c>
+      <c r="G39">
         <v>7</v>
       </c>
-      <c r="H35" t="s">
-        <v>82</v>
-      </c>
-      <c r="I35" t="s">
+      <c r="H39" t="s">
+        <v>82</v>
+      </c>
+      <c r="I39" t="s">
         <v>40</v>
       </c>
     </row>
@@ -61407,35 +61577,35 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -61445,502 +61615,711 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B2" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C2" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C3" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B4" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C4" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B5" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C5" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C6" t="s">
         <v>113</v>
-      </c>
-      <c r="C6" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B7" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C7" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B8" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C8" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B9" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C9" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B10" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C10" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B11" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C11" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B12" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="C12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B13" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C13" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B14" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="C14" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B15" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="C15" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B16" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="C16" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B17" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C17" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B18" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="C18" t="s">
-        <v>138</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B19" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C19" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B20" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C20" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B21" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C21" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
+        <v>150</v>
+      </c>
+      <c r="B22" t="s">
         <v>145</v>
       </c>
-      <c r="B22" t="s">
-        <v>146</v>
-      </c>
       <c r="C22" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B23" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C23" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B24" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C24" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B25" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C25" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B26" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C26" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B27" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C27" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B28" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C28" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B29" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C29" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B30" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C30" t="s">
-        <v>163</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B31" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C31" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B32" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C32" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B33" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C33" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B34" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C34" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B35" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C35" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B36" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C36" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B37" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C37" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B38" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C38" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B39" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C39" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B40" t="s">
-        <v>115</v>
+        <v>186</v>
       </c>
       <c r="C40" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B41" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C41" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B42" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C42" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B43" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C43" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B44" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C44" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B45" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C45" t="s">
-        <v>163</v>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
+        <v>197</v>
+      </c>
+      <c r="B46" t="s">
+        <v>198</v>
+      </c>
+      <c r="C46" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
+        <v>199</v>
+      </c>
+      <c r="B47" t="s">
+        <v>200</v>
+      </c>
+      <c r="C47" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
+        <v>202</v>
+      </c>
+      <c r="B48" t="s">
+        <v>203</v>
+      </c>
+      <c r="C48" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
+        <v>204</v>
+      </c>
+      <c r="B49" t="s">
+        <v>205</v>
+      </c>
+      <c r="C49" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
+        <v>206</v>
+      </c>
+      <c r="B50" t="s">
+        <v>207</v>
+      </c>
+      <c r="C50" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" t="s">
+        <v>208</v>
+      </c>
+      <c r="B51" t="s">
+        <v>209</v>
+      </c>
+      <c r="C51" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" t="s">
+        <v>210</v>
+      </c>
+      <c r="B52" t="s">
+        <v>211</v>
+      </c>
+      <c r="C52" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" t="s">
+        <v>212</v>
+      </c>
+      <c r="B53" t="s">
+        <v>213</v>
+      </c>
+      <c r="C53" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" t="s">
+        <v>214</v>
+      </c>
+      <c r="B54" t="s">
+        <v>215</v>
+      </c>
+      <c r="C54" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" t="s">
+        <v>216</v>
+      </c>
+      <c r="B55" t="s">
+        <v>217</v>
+      </c>
+      <c r="C55" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" t="s">
+        <v>218</v>
+      </c>
+      <c r="B56" t="s">
+        <v>219</v>
+      </c>
+      <c r="C56" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" t="s">
+        <v>220</v>
+      </c>
+      <c r="B57" t="s">
+        <v>221</v>
+      </c>
+      <c r="C57" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" t="s">
+        <v>222</v>
+      </c>
+      <c r="B58" t="s">
+        <v>223</v>
+      </c>
+      <c r="C58" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" t="s">
+        <v>224</v>
+      </c>
+      <c r="B59" t="s">
+        <v>139</v>
+      </c>
+      <c r="C59" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" t="s">
+        <v>225</v>
+      </c>
+      <c r="B60" t="s">
+        <v>226</v>
+      </c>
+      <c r="C60" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" t="s">
+        <v>227</v>
+      </c>
+      <c r="B61" t="s">
+        <v>228</v>
+      </c>
+      <c r="C61" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" t="s">
+        <v>229</v>
+      </c>
+      <c r="B62" t="s">
+        <v>230</v>
+      </c>
+      <c r="C62" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" t="s">
+        <v>231</v>
+      </c>
+      <c r="B63" t="s">
+        <v>232</v>
+      </c>
+      <c r="C63" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" t="s">
+        <v>233</v>
+      </c>
+      <c r="B64" t="s">
+        <v>234</v>
+      </c>
+      <c r="C64" t="s">
+        <v>201</v>
       </c>
     </row>
   </sheetData>

--- a/04_Network/04_Associate/c_data/04_associate.xlsx
+++ b/04_Network/04_Associate/c_data/04_associate.xlsx
@@ -32,7 +32,7 @@
     <t>counts</t>
   </si>
   <si>
-    <t>Tested, p &lt; 0.05 and BH &lt; 0.05 counts per model term and trait, and per window and outcome.</t>
+    <t>Tested, p &lt; 0.05 and BH &lt; 0.05 counts per term and trait, and per window and outcome.</t>
   </si>
   <si>
     <t>model</t>
